--- a/data/Symptom Coding JL 20250203.xlsx
+++ b/data/Symptom Coding JL 20250203.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jlangfus\nosync\content-overlap\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8204D39-FD92-44E0-AC42-C440EA781829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FAAEAD2-E8F2-4D7F-A813-571707335F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26040" yWindow="-21870" windowWidth="21420" windowHeight="20985" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item List" sheetId="1" r:id="rId1"/>
@@ -1415,7 +1415,7 @@
     <t>IA_Diary</t>
   </si>
   <si>
-    <t>SQA_CD</t>
+    <t>SDQ_CD</t>
   </si>
 </sst>
 </file>
@@ -1633,16 +1633,19 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1650,11 +1653,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1875,14 +1875,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D223"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" customWidth="1"/>
-    <col min="2" max="2" width="5.42578125" customWidth="1"/>
-    <col min="3" max="3" width="115.7109375" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+    <col min="2" max="2" width="5.44140625" customWidth="1"/>
+    <col min="3" max="3" width="115.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>3</v>
       </c>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>3</v>
       </c>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>3</v>
       </c>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>3</v>
       </c>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>3</v>
       </c>
@@ -2086,13 +2086,13 @@
       </c>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>20</v>
       </c>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>20</v>
       </c>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D25" s="2"/>
     </row>
-    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>20</v>
       </c>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>20</v>
       </c>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="D27" s="2"/>
     </row>
-    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>20</v>
       </c>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>20</v>
       </c>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D29" s="2"/>
     </row>
-    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>20</v>
       </c>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>20</v>
       </c>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="D31" s="2"/>
     </row>
-    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>20</v>
       </c>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>20</v>
       </c>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="D33" s="2"/>
     </row>
-    <row r="34" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>20</v>
       </c>
@@ -2284,13 +2284,13 @@
       </c>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
     </row>
-    <row r="36" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>37</v>
       </c>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>39</v>
       </c>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="D37" s="2"/>
     </row>
-    <row r="38" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>37</v>
       </c>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>39</v>
       </c>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="D39" s="2"/>
     </row>
-    <row r="40" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>37</v>
       </c>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D40" s="2"/>
     </row>
-    <row r="41" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>39</v>
       </c>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="D41" s="2"/>
     </row>
-    <row r="42" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>37</v>
       </c>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="D42" s="2"/>
     </row>
-    <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>37</v>
       </c>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="D43" s="2"/>
     </row>
-    <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>39</v>
       </c>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>39</v>
       </c>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>37</v>
       </c>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>39</v>
       </c>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="D47" s="2"/>
     </row>
-    <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>37</v>
       </c>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>37</v>
       </c>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D49" s="2"/>
     </row>
-    <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>39</v>
       </c>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>37</v>
       </c>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="D51" s="2"/>
     </row>
-    <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>39</v>
       </c>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>39</v>
       </c>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D53" s="2"/>
     </row>
-    <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>37</v>
       </c>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>39</v>
       </c>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="D55" s="2"/>
     </row>
-    <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>39</v>
       </c>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D56" s="2"/>
     </row>
-    <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>37</v>
       </c>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="D57" s="2"/>
     </row>
-    <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>39</v>
       </c>
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D58" s="2"/>
     </row>
-    <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
     </row>
-    <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
     </row>
-    <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>62</v>
       </c>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="D61" s="2"/>
     </row>
-    <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>62</v>
       </c>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="D62" s="2"/>
     </row>
-    <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>62</v>
       </c>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="D63" s="2"/>
     </row>
-    <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>62</v>
       </c>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="D64" s="2"/>
     </row>
-    <row r="65" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>62</v>
       </c>
@@ -2638,7 +2638,7 @@
       </c>
       <c r="D65" s="2"/>
     </row>
-    <row r="66" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>62</v>
       </c>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D66" s="2"/>
     </row>
-    <row r="67" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>62</v>
       </c>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="D67" s="2"/>
     </row>
-    <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>62</v>
       </c>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D68" s="2"/>
     </row>
-    <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>62</v>
       </c>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="D69" s="2"/>
     </row>
-    <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>62</v>
       </c>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="D70" s="2"/>
     </row>
-    <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>62</v>
       </c>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="D71" s="2"/>
     </row>
-    <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>62</v>
       </c>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="D72" s="2"/>
     </row>
-    <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>62</v>
       </c>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="D73" s="2"/>
     </row>
-    <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>62</v>
       </c>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="D74" s="2"/>
     </row>
-    <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>62</v>
       </c>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="D75" s="2"/>
     </row>
-    <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>62</v>
       </c>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="D76" s="2"/>
     </row>
-    <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>62</v>
       </c>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="D77" s="2"/>
     </row>
-    <row r="78" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>62</v>
       </c>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="D78" s="2"/>
     </row>
-    <row r="79" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>62</v>
       </c>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="D79" s="2"/>
     </row>
-    <row r="80" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>62</v>
       </c>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="D80" s="2"/>
     </row>
-    <row r="81" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>62</v>
       </c>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D81" s="2"/>
     </row>
-    <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>62</v>
       </c>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="D82" s="2"/>
     </row>
-    <row r="83" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>62</v>
       </c>
@@ -2854,13 +2854,13 @@
       </c>
       <c r="D83" s="2"/>
     </row>
-    <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
     </row>
-    <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>86</v>
       </c>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="D85" s="2"/>
     </row>
-    <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>86</v>
       </c>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D86" s="2"/>
     </row>
-    <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>86</v>
       </c>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D87" s="2"/>
     </row>
-    <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>86</v>
       </c>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D88" s="2"/>
     </row>
-    <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>86</v>
       </c>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="D89" s="2"/>
     </row>
-    <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>86</v>
       </c>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D90" s="2"/>
     </row>
-    <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>86</v>
       </c>
@@ -2944,13 +2944,13 @@
       </c>
       <c r="D91" s="2"/>
     </row>
-    <row r="92" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
     </row>
-    <row r="93" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>94</v>
       </c>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="D93" s="2"/>
     </row>
-    <row r="94" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>94</v>
       </c>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="D94" s="2"/>
     </row>
-    <row r="95" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>94</v>
       </c>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D95" s="2"/>
     </row>
-    <row r="96" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>94</v>
       </c>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D96" s="2"/>
     </row>
-    <row r="97" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>94</v>
       </c>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="D97" s="2"/>
     </row>
-    <row r="98" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>94</v>
       </c>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="D98" s="2"/>
     </row>
-    <row r="99" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>94</v>
       </c>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D99" s="2"/>
     </row>
-    <row r="100" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>94</v>
       </c>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D100" s="2"/>
     </row>
-    <row r="101" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>94</v>
       </c>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="D101" s="2"/>
     </row>
-    <row r="102" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>94</v>
       </c>
@@ -3070,13 +3070,13 @@
       </c>
       <c r="D102" s="2"/>
     </row>
-    <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
     </row>
-    <row r="104" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>103</v>
       </c>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="D104" s="2"/>
     </row>
-    <row r="105" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>103</v>
       </c>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="D105" s="2"/>
     </row>
-    <row r="106" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>103</v>
       </c>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="D106" s="2"/>
     </row>
-    <row r="107" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>103</v>
       </c>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="D107" s="2"/>
     </row>
-    <row r="108" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>103</v>
       </c>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="D108" s="2"/>
     </row>
-    <row r="109" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>103</v>
       </c>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="D109" s="2"/>
     </row>
-    <row r="110" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>103</v>
       </c>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D110" s="2"/>
     </row>
-    <row r="111" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>103</v>
       </c>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="D111" s="2"/>
     </row>
-    <row r="112" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>103</v>
       </c>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="D112" s="2"/>
     </row>
-    <row r="113" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>103</v>
       </c>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="D113" s="2"/>
     </row>
-    <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>103</v>
       </c>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="D114" s="2"/>
     </row>
-    <row r="115" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>103</v>
       </c>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="D115" s="2"/>
     </row>
-    <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>103</v>
       </c>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="D116" s="2"/>
     </row>
-    <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>103</v>
       </c>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="D117" s="2"/>
     </row>
-    <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>103</v>
       </c>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="D118" s="2"/>
     </row>
-    <row r="119" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>103</v>
       </c>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D119" s="2"/>
     </row>
-    <row r="120" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>103</v>
       </c>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="D120" s="2"/>
     </row>
-    <row r="121" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>103</v>
       </c>
@@ -3292,13 +3292,13 @@
       </c>
       <c r="D121" s="2"/>
     </row>
-    <row r="122" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
     </row>
-    <row r="123" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>120</v>
       </c>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="D123" s="2"/>
     </row>
-    <row r="124" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>120</v>
       </c>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D124" s="2"/>
     </row>
-    <row r="125" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>120</v>
       </c>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="D125" s="2"/>
     </row>
-    <row r="126" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>120</v>
       </c>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="D126" s="2"/>
     </row>
-    <row r="127" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>120</v>
       </c>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="D127" s="2"/>
     </row>
-    <row r="128" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>120</v>
       </c>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="D128" s="2"/>
     </row>
-    <row r="129" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>120</v>
       </c>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="D129" s="2"/>
     </row>
-    <row r="130" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>120</v>
       </c>
@@ -3394,13 +3394,13 @@
       </c>
       <c r="D130" s="2"/>
     </row>
-    <row r="131" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
       <c r="D131" s="2"/>
     </row>
-    <row r="132" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>129</v>
       </c>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="D132" s="2"/>
     </row>
-    <row r="133" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>129</v>
       </c>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="D133" s="2"/>
     </row>
-    <row r="134" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>129</v>
       </c>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="D134" s="2"/>
     </row>
-    <row r="135" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>129</v>
       </c>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="D135" s="2"/>
     </row>
-    <row r="136" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>129</v>
       </c>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="D136" s="2"/>
     </row>
-    <row r="137" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>129</v>
       </c>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D137" s="2"/>
     </row>
-    <row r="138" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>129</v>
       </c>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="D138" s="2"/>
     </row>
-    <row r="139" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>129</v>
       </c>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="D139" s="2"/>
     </row>
-    <row r="140" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>129</v>
       </c>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="D140" s="2"/>
     </row>
-    <row r="141" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>129</v>
       </c>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="D141" s="2"/>
     </row>
-    <row r="142" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>129</v>
       </c>
@@ -3532,7 +3532,7 @@
       </c>
       <c r="D142" s="2"/>
     </row>
-    <row r="143" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>129</v>
       </c>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="D143" s="2"/>
     </row>
-    <row r="144" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>129</v>
       </c>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D144" s="2"/>
     </row>
-    <row r="145" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>129</v>
       </c>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="D145" s="2"/>
     </row>
-    <row r="146" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>129</v>
       </c>
@@ -3580,13 +3580,13 @@
       </c>
       <c r="D146" s="2"/>
     </row>
-    <row r="147" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
     </row>
-    <row r="148" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>145</v>
       </c>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D148" s="2"/>
     </row>
-    <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>145</v>
       </c>
@@ -3610,13 +3610,13 @@
       </c>
       <c r="D149" s="2"/>
     </row>
-    <row r="150" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
     </row>
-    <row r="151" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>148</v>
       </c>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="D151" s="2"/>
     </row>
-    <row r="152" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>148</v>
       </c>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D152" s="2"/>
     </row>
-    <row r="153" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>148</v>
       </c>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="D153" s="2"/>
     </row>
-    <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>148</v>
       </c>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="D154" s="2"/>
     </row>
-    <row r="155" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>148</v>
       </c>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="D155" s="2"/>
     </row>
-    <row r="156" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>148</v>
       </c>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="D156" s="2"/>
     </row>
-    <row r="157" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>148</v>
       </c>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="D157" s="2"/>
     </row>
-    <row r="158" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>148</v>
       </c>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="D158" s="2"/>
     </row>
-    <row r="159" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>148</v>
       </c>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D159" s="2"/>
     </row>
-    <row r="160" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>148</v>
       </c>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="D160" s="2"/>
     </row>
-    <row r="161" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>148</v>
       </c>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="D161" s="2"/>
     </row>
-    <row r="162" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>148</v>
       </c>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="D162" s="2"/>
     </row>
-    <row r="163" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>148</v>
       </c>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="D163" s="2"/>
     </row>
-    <row r="164" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>148</v>
       </c>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D164" s="2"/>
     </row>
-    <row r="165" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>148</v>
       </c>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="D165" s="2"/>
     </row>
-    <row r="166" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>148</v>
       </c>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="D166" s="2"/>
     </row>
-    <row r="167" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>148</v>
       </c>
@@ -3820,13 +3820,13 @@
       </c>
       <c r="D167" s="2"/>
     </row>
-    <row r="168" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
       <c r="D168" s="2"/>
     </row>
-    <row r="169" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>166</v>
       </c>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="D169" s="2"/>
     </row>
-    <row r="170" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>166</v>
       </c>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="D170" s="2"/>
     </row>
-    <row r="171" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>166</v>
       </c>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="D171" s="2"/>
     </row>
-    <row r="172" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>166</v>
       </c>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="D172" s="2"/>
     </row>
-    <row r="173" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>166</v>
       </c>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="D173" s="2"/>
     </row>
-    <row r="174" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>166</v>
       </c>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D174" s="2"/>
     </row>
-    <row r="175" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>166</v>
       </c>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="D175" s="2"/>
     </row>
-    <row r="176" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>166</v>
       </c>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D176" s="2"/>
     </row>
-    <row r="177" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>166</v>
       </c>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="D177" s="2"/>
     </row>
-    <row r="178" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>166</v>
       </c>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="D178" s="2"/>
     </row>
-    <row r="179" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>166</v>
       </c>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="D179" s="2"/>
     </row>
-    <row r="180" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>166</v>
       </c>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="D180" s="2"/>
     </row>
-    <row r="181" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>166</v>
       </c>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="D181" s="2"/>
     </row>
-    <row r="182" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>166</v>
       </c>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="D182" s="2"/>
     </row>
-    <row r="183" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>166</v>
       </c>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D183" s="2"/>
     </row>
-    <row r="184" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>166</v>
       </c>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="D184" s="2"/>
     </row>
-    <row r="185" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>166</v>
       </c>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D185" s="2"/>
     </row>
-    <row r="186" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>166</v>
       </c>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="D186" s="2"/>
     </row>
-    <row r="187" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>166</v>
       </c>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="D187" s="2"/>
     </row>
-    <row r="188" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>166</v>
       </c>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="D188" s="2"/>
     </row>
-    <row r="189" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>166</v>
       </c>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="D189" s="2"/>
     </row>
-    <row r="190" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>166</v>
       </c>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="D190" s="2"/>
     </row>
-    <row r="191" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>166</v>
       </c>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="D191" s="2"/>
     </row>
-    <row r="192" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>166</v>
       </c>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="D192" s="2"/>
     </row>
-    <row r="193" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>166</v>
       </c>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="D193" s="2"/>
     </row>
-    <row r="194" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>166</v>
       </c>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="D194" s="2"/>
     </row>
-    <row r="195" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>166</v>
       </c>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="D195" s="2"/>
     </row>
-    <row r="196" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>166</v>
       </c>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D196" s="2"/>
     </row>
-    <row r="197" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>166</v>
       </c>
@@ -4174,13 +4174,13 @@
       </c>
       <c r="D197" s="2"/>
     </row>
-    <row r="198" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
     </row>
-    <row r="199" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>196</v>
       </c>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="D199" s="2"/>
     </row>
-    <row r="200" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>196</v>
       </c>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="D200" s="2"/>
     </row>
-    <row r="201" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>196</v>
       </c>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="D201" s="2"/>
     </row>
-    <row r="202" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>196</v>
       </c>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="D202" s="2"/>
     </row>
-    <row r="203" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>196</v>
       </c>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="D203" s="2"/>
     </row>
-    <row r="204" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>196</v>
       </c>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D204" s="2"/>
     </row>
-    <row r="205" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>196</v>
       </c>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="D205" s="2"/>
     </row>
-    <row r="206" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>196</v>
       </c>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="D206" s="2"/>
     </row>
-    <row r="207" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>196</v>
       </c>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="D207" s="2"/>
     </row>
-    <row r="208" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>196</v>
       </c>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="D208" s="2"/>
     </row>
-    <row r="209" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>196</v>
       </c>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="D209" s="2"/>
     </row>
-    <row r="210" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>196</v>
       </c>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="D210" s="2"/>
     </row>
-    <row r="211" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>196</v>
       </c>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="D211" s="2"/>
     </row>
-    <row r="212" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>196</v>
       </c>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="D212" s="2"/>
     </row>
-    <row r="213" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>196</v>
       </c>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="D213" s="2"/>
     </row>
-    <row r="215" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A215" s="7" t="s">
         <v>212</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A216" s="7" t="s">
         <v>212</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A217" s="7" t="s">
         <v>212</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="218" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A218" s="7" t="s">
         <v>212</v>
       </c>
@@ -4404,7 +4404,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="219" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A219" s="7" t="s">
         <v>212</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="220" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A220" s="7" t="s">
         <v>212</v>
       </c>
@@ -4426,7 +4426,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="221" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
         <v>212</v>
       </c>
@@ -4437,7 +4437,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="222" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A222" s="7" t="s">
         <v>212</v>
       </c>
@@ -4448,7 +4448,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="223" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A223" s="7" t="s">
         <v>212</v>
       </c>
@@ -4470,15 +4470,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D225"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" customWidth="1"/>
-    <col min="2" max="2" width="5.42578125" customWidth="1"/>
-    <col min="3" max="3" width="115.7109375" style="13" customWidth="1"/>
-    <col min="4" max="4" width="31.42578125" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+    <col min="2" max="2" width="5.44140625" customWidth="1"/>
+    <col min="3" max="3" width="115.6640625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="31.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4492,7 +4492,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -4506,7 +4506,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -4520,7 +4520,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -4548,7 +4548,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -4562,7 +4562,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
@@ -4590,7 +4590,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
@@ -4604,7 +4604,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>3</v>
       </c>
@@ -4646,7 +4646,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>3</v>
       </c>
@@ -4660,7 +4660,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>3</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>3</v>
       </c>
@@ -4688,7 +4688,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>3</v>
       </c>
@@ -4702,7 +4702,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>3</v>
       </c>
@@ -4716,13 +4716,13 @@
         <v>223</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="11"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>20</v>
       </c>
@@ -4736,7 +4736,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>20</v>
       </c>
@@ -4750,7 +4750,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -4764,7 +4764,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
@@ -4778,7 +4778,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>20</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>20</v>
       </c>
@@ -4806,7 +4806,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>20</v>
       </c>
@@ -4820,7 +4820,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>20</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>20</v>
       </c>
@@ -4848,7 +4848,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>20</v>
       </c>
@@ -4862,7 +4862,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>20</v>
       </c>
@@ -4876,7 +4876,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>20</v>
       </c>
@@ -4890,7 +4890,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>20</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>20</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>20</v>
       </c>
@@ -4932,7 +4932,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>20</v>
       </c>
@@ -4946,13 +4946,13 @@
         <v>229</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="11"/>
       <c r="D35" s="2"/>
     </row>
-    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>37</v>
       </c>
@@ -4966,7 +4966,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>39</v>
       </c>
@@ -4980,7 +4980,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>37</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>39</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>37</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>39</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>37</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>37</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>39</v>
       </c>
@@ -5078,7 +5078,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>39</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>37</v>
       </c>
@@ -5106,7 +5106,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>39</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>37</v>
       </c>
@@ -5134,7 +5134,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>37</v>
       </c>
@@ -5148,7 +5148,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>39</v>
       </c>
@@ -5162,7 +5162,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>37</v>
       </c>
@@ -5176,7 +5176,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>39</v>
       </c>
@@ -5190,7 +5190,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="53" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>39</v>
       </c>
@@ -5204,7 +5204,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="54" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>37</v>
       </c>
@@ -5218,7 +5218,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>39</v>
       </c>
@@ -5232,7 +5232,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="56" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>39</v>
       </c>
@@ -5246,7 +5246,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>37</v>
       </c>
@@ -5260,7 +5260,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>39</v>
       </c>
@@ -5274,19 +5274,19 @@
         <v>224</v>
       </c>
     </row>
-    <row r="59" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="11"/>
       <c r="D59" s="2"/>
     </row>
-    <row r="60" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="11"/>
       <c r="D60" s="2"/>
     </row>
-    <row r="61" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>62</v>
       </c>
@@ -5300,7 +5300,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="62" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>62</v>
       </c>
@@ -5314,7 +5314,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="63" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>62</v>
       </c>
@@ -5328,7 +5328,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="64" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>62</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>62</v>
       </c>
@@ -5356,7 +5356,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="66" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>62</v>
       </c>
@@ -5370,7 +5370,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="67" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>62</v>
       </c>
@@ -5384,7 +5384,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="68" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>62</v>
       </c>
@@ -5398,7 +5398,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="69" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>62</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="70" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>62</v>
       </c>
@@ -5426,7 +5426,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="71" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>62</v>
       </c>
@@ -5440,7 +5440,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="72" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>62</v>
       </c>
@@ -5454,7 +5454,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>62</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="74" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>62</v>
       </c>
@@ -5482,7 +5482,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>62</v>
       </c>
@@ -5496,7 +5496,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>62</v>
       </c>
@@ -5510,7 +5510,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>62</v>
       </c>
@@ -5524,7 +5524,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>62</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>62</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="80" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>62</v>
       </c>
@@ -5566,7 +5566,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>62</v>
       </c>
@@ -5580,7 +5580,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>62</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>62</v>
       </c>
@@ -5608,13 +5608,13 @@
         <v>225</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="11"/>
       <c r="D84" s="2"/>
     </row>
-    <row r="85" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>86</v>
       </c>
@@ -5628,7 +5628,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>86</v>
       </c>
@@ -5642,7 +5642,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>86</v>
       </c>
@@ -5656,7 +5656,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="88" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>86</v>
       </c>
@@ -5670,7 +5670,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>86</v>
       </c>
@@ -5684,7 +5684,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>86</v>
       </c>
@@ -5698,7 +5698,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="91" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>86</v>
       </c>
@@ -5712,13 +5712,13 @@
         <v>223</v>
       </c>
     </row>
-    <row r="92" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="11"/>
       <c r="D92" s="2"/>
     </row>
-    <row r="93" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>94</v>
       </c>
@@ -5732,7 +5732,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="94" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>94</v>
       </c>
@@ -5746,7 +5746,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>94</v>
       </c>
@@ -5760,7 +5760,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>94</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>94</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>94</v>
       </c>
@@ -5802,7 +5802,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="99" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>94</v>
       </c>
@@ -5816,7 +5816,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="100" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>94</v>
       </c>
@@ -5830,7 +5830,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>94</v>
       </c>
@@ -5844,7 +5844,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="102" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>94</v>
       </c>
@@ -5858,13 +5858,13 @@
         <v>224</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="11"/>
       <c r="D103" s="2"/>
     </row>
-    <row r="104" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>103</v>
       </c>
@@ -5878,7 +5878,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>103</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="106" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>103</v>
       </c>
@@ -5906,7 +5906,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="107" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>103</v>
       </c>
@@ -5920,7 +5920,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="108" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>103</v>
       </c>
@@ -5934,7 +5934,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="109" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>103</v>
       </c>
@@ -5948,7 +5948,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="110" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>103</v>
       </c>
@@ -5962,7 +5962,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>103</v>
       </c>
@@ -5976,7 +5976,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>103</v>
       </c>
@@ -5990,7 +5990,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="113" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>103</v>
       </c>
@@ -6004,7 +6004,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="114" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>103</v>
       </c>
@@ -6018,7 +6018,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>103</v>
       </c>
@@ -6032,7 +6032,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>103</v>
       </c>
@@ -6046,7 +6046,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="117" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>103</v>
       </c>
@@ -6060,7 +6060,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>103</v>
       </c>
@@ -6074,7 +6074,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="119" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>103</v>
       </c>
@@ -6088,7 +6088,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="120" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>103</v>
       </c>
@@ -6102,7 +6102,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="121" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>103</v>
       </c>
@@ -6116,13 +6116,13 @@
         <v>224</v>
       </c>
     </row>
-    <row r="122" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="11"/>
       <c r="D122" s="2"/>
     </row>
-    <row r="123" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>166</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>166</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>166</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="126" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>166</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>166</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>166</v>
       </c>
@@ -6206,7 +6206,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>166</v>
       </c>
@@ -6220,7 +6220,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="130" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>166</v>
       </c>
@@ -6234,7 +6234,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="131" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>166</v>
       </c>
@@ -6248,7 +6248,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="132" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>166</v>
       </c>
@@ -6262,7 +6262,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="133" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>166</v>
       </c>
@@ -6276,7 +6276,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="134" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>166</v>
       </c>
@@ -6290,7 +6290,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>166</v>
       </c>
@@ -6304,7 +6304,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="136" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>166</v>
       </c>
@@ -6318,7 +6318,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="137" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>166</v>
       </c>
@@ -6332,7 +6332,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="138" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>166</v>
       </c>
@@ -6346,7 +6346,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="139" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>166</v>
       </c>
@@ -6360,7 +6360,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>166</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="141" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>166</v>
       </c>
@@ -6388,7 +6388,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="142" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>166</v>
       </c>
@@ -6402,7 +6402,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="143" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>166</v>
       </c>
@@ -6416,7 +6416,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="144" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>166</v>
       </c>
@@ -6430,7 +6430,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>166</v>
       </c>
@@ -6444,7 +6444,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>166</v>
       </c>
@@ -6458,7 +6458,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="147" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>166</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="148" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>166</v>
       </c>
@@ -6486,7 +6486,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="149" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>166</v>
       </c>
@@ -6500,7 +6500,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="150" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>166</v>
       </c>
@@ -6514,7 +6514,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="151" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>166</v>
       </c>
@@ -6528,13 +6528,13 @@
         <v>240</v>
       </c>
     </row>
-    <row r="152" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="11"/>
       <c r="D152" s="2"/>
     </row>
-    <row r="153" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>196</v>
       </c>
@@ -6548,7 +6548,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="154" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>196</v>
       </c>
@@ -6562,7 +6562,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="155" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>196</v>
       </c>
@@ -6576,7 +6576,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="156" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>196</v>
       </c>
@@ -6590,7 +6590,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="157" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>196</v>
       </c>
@@ -6604,7 +6604,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="158" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>196</v>
       </c>
@@ -6618,7 +6618,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="159" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>196</v>
       </c>
@@ -6632,7 +6632,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="160" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>196</v>
       </c>
@@ -6646,7 +6646,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="161" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>196</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="162" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>196</v>
       </c>
@@ -6674,7 +6674,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>196</v>
       </c>
@@ -6688,7 +6688,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>196</v>
       </c>
@@ -6702,7 +6702,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="165" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>196</v>
       </c>
@@ -6716,7 +6716,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="166" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>196</v>
       </c>
@@ -6730,7 +6730,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="167" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>196</v>
       </c>
@@ -6744,7 +6744,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="171" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
         <v>212</v>
       </c>
@@ -6755,7 +6755,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="172" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A172" s="7" t="s">
         <v>212</v>
       </c>
@@ -6766,7 +6766,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="173" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
         <v>212</v>
       </c>
@@ -6777,7 +6777,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="174" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A174" s="7" t="s">
         <v>212</v>
       </c>
@@ -6788,7 +6788,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="175" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
         <v>212</v>
       </c>
@@ -6799,7 +6799,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="176" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
         <v>212</v>
       </c>
@@ -6810,7 +6810,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
         <v>212</v>
       </c>
@@ -6821,7 +6821,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A178" s="7" t="s">
         <v>212</v>
       </c>
@@ -6832,7 +6832,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
         <v>212</v>
       </c>
@@ -6843,7 +6843,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>120</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>120</v>
       </c>
@@ -6865,7 +6865,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>120</v>
       </c>
@@ -6876,7 +6876,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>120</v>
       </c>
@@ -6887,7 +6887,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>120</v>
       </c>
@@ -6898,7 +6898,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>120</v>
       </c>
@@ -6909,7 +6909,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>120</v>
       </c>
@@ -6920,7 +6920,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>120</v>
       </c>
@@ -6931,12 +6931,12 @@
         <v>128</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="11"/>
     </row>
-    <row r="190" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>129</v>
       </c>
@@ -6947,7 +6947,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>129</v>
       </c>
@@ -6958,7 +6958,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>129</v>
       </c>
@@ -6969,7 +6969,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>129</v>
       </c>
@@ -6980,7 +6980,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>129</v>
       </c>
@@ -6991,7 +6991,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>129</v>
       </c>
@@ -7002,7 +7002,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>129</v>
       </c>
@@ -7013,7 +7013,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>129</v>
       </c>
@@ -7024,7 +7024,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>129</v>
       </c>
@@ -7035,7 +7035,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>129</v>
       </c>
@@ -7046,7 +7046,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>129</v>
       </c>
@@ -7057,7 +7057,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>129</v>
       </c>
@@ -7068,7 +7068,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>129</v>
       </c>
@@ -7079,7 +7079,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>129</v>
       </c>
@@ -7090,7 +7090,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>129</v>
       </c>
@@ -7101,12 +7101,12 @@
         <v>144</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="11"/>
     </row>
-    <row r="206" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>145</v>
       </c>
@@ -7117,7 +7117,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>145</v>
       </c>
@@ -7128,12 +7128,12 @@
         <v>147</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="11"/>
     </row>
-    <row r="209" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>148</v>
       </c>
@@ -7144,7 +7144,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>148</v>
       </c>
@@ -7155,7 +7155,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>148</v>
       </c>
@@ -7166,7 +7166,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>148</v>
       </c>
@@ -7177,7 +7177,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>148</v>
       </c>
@@ -7188,7 +7188,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>148</v>
       </c>
@@ -7199,7 +7199,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>148</v>
       </c>
@@ -7210,7 +7210,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>148</v>
       </c>
@@ -7221,7 +7221,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>148</v>
       </c>
@@ -7232,7 +7232,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>148</v>
       </c>
@@ -7243,7 +7243,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>148</v>
       </c>
@@ -7254,7 +7254,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>148</v>
       </c>
@@ -7265,7 +7265,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>148</v>
       </c>
@@ -7276,7 +7276,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>148</v>
       </c>
@@ -7287,7 +7287,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>148</v>
       </c>
@@ -7298,7 +7298,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>148</v>
       </c>
@@ -7309,7 +7309,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>148</v>
       </c>
@@ -7331,14 +7331,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:G225"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" style="20" customWidth="1"/>
-    <col min="2" max="2" width="5.42578125" style="20" customWidth="1"/>
-    <col min="3" max="3" width="115.7109375" style="21" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" style="21" customWidth="1"/>
-    <col min="5" max="5" width="31.42578125" style="20" customWidth="1"/>
-    <col min="8" max="8" width="42.5703125" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" style="20" customWidth="1"/>
+    <col min="2" max="2" width="5.44140625" style="20" customWidth="1"/>
+    <col min="3" max="3" width="115.6640625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="31.44140625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="42.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7358,7 +7358,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>3</v>
       </c>
@@ -7375,7 +7375,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>3</v>
       </c>
@@ -7392,7 +7392,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>3</v>
       </c>
@@ -7409,7 +7409,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>3</v>
       </c>
@@ -7426,7 +7426,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
         <v>3</v>
       </c>
@@ -7443,7 +7443,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>3</v>
       </c>
@@ -7460,7 +7460,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>3</v>
       </c>
@@ -7477,7 +7477,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>3</v>
       </c>
@@ -7494,7 +7494,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
         <v>3</v>
       </c>
@@ -7511,7 +7511,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>3</v>
       </c>
@@ -7528,7 +7528,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
         <v>3</v>
       </c>
@@ -7545,7 +7545,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>3</v>
       </c>
@@ -7562,7 +7562,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
         <v>3</v>
       </c>
@@ -7579,7 +7579,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>3</v>
       </c>
@@ -7596,7 +7596,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>3</v>
       </c>
@@ -7613,7 +7613,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>3</v>
       </c>
@@ -7630,14 +7630,14 @@
         <v>226</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="18"/>
       <c r="B18" s="18"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
       <c r="E18" s="18"/>
     </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>20</v>
       </c>
@@ -7654,7 +7654,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
         <v>20</v>
       </c>
@@ -7671,7 +7671,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
         <v>20</v>
       </c>
@@ -7688,7 +7688,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
         <v>20</v>
       </c>
@@ -7705,7 +7705,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
         <v>20</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
         <v>20</v>
       </c>
@@ -7739,7 +7739,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>20</v>
       </c>
@@ -7756,7 +7756,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
         <v>20</v>
       </c>
@@ -7773,7 +7773,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
         <v>20</v>
       </c>
@@ -7790,7 +7790,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
         <v>20</v>
       </c>
@@ -7807,7 +7807,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
         <v>20</v>
       </c>
@@ -7824,7 +7824,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
         <v>20</v>
       </c>
@@ -7841,7 +7841,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="18" t="s">
         <v>20</v>
       </c>
@@ -7858,7 +7858,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
         <v>20</v>
       </c>
@@ -7875,7 +7875,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
         <v>20</v>
       </c>
@@ -7892,7 +7892,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
         <v>20</v>
       </c>
@@ -7909,14 +7909,14 @@
         <v>229</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="18"/>
       <c r="B35" s="18"/>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>
       <c r="E35" s="18"/>
     </row>
-    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="18" t="s">
         <v>37</v>
       </c>
@@ -7933,7 +7933,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="18" t="s">
         <v>39</v>
       </c>
@@ -7950,7 +7950,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="18" t="s">
         <v>39</v>
       </c>
@@ -7967,7 +7967,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="18" t="s">
         <v>39</v>
       </c>
@@ -7984,7 +7984,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="18" t="s">
         <v>37</v>
       </c>
@@ -8001,7 +8001,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="18" t="s">
         <v>37</v>
       </c>
@@ -8018,7 +8018,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="s">
         <v>37</v>
       </c>
@@ -8035,7 +8035,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A43" s="18" t="s">
         <v>37</v>
       </c>
@@ -8052,7 +8052,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="18" t="s">
         <v>37</v>
       </c>
@@ -8069,7 +8069,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A45" s="18" t="s">
         <v>37</v>
       </c>
@@ -8086,7 +8086,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A46" s="18" t="s">
         <v>39</v>
       </c>
@@ -8103,7 +8103,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A47" s="18" t="s">
         <v>37</v>
       </c>
@@ -8120,7 +8120,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
         <v>39</v>
       </c>
@@ -8137,7 +8137,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A49" s="18" t="s">
         <v>37</v>
       </c>
@@ -8154,7 +8154,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A50" s="18" t="s">
         <v>39</v>
       </c>
@@ -8171,7 +8171,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A51" s="18" t="s">
         <v>39</v>
       </c>
@@ -8188,7 +8188,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A52" s="18" t="s">
         <v>39</v>
       </c>
@@ -8205,7 +8205,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A53" s="18" t="s">
         <v>39</v>
       </c>
@@ -8222,7 +8222,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A54" s="18" t="s">
         <v>39</v>
       </c>
@@ -8239,7 +8239,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A55" s="18" t="s">
         <v>37</v>
       </c>
@@ -8256,7 +8256,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A56" s="18" t="s">
         <v>39</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A57" s="18" t="s">
         <v>39</v>
       </c>
@@ -8290,7 +8290,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A58" s="18" t="s">
         <v>37</v>
       </c>
@@ -8307,21 +8307,21 @@
         <v>226</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A59" s="18"/>
       <c r="B59" s="18"/>
       <c r="C59" s="14"/>
       <c r="D59" s="14"/>
       <c r="E59" s="18"/>
     </row>
-    <row r="60" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A60" s="18"/>
       <c r="B60" s="18"/>
       <c r="C60" s="14"/>
       <c r="D60" s="14"/>
       <c r="E60" s="18"/>
     </row>
-    <row r="61" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A61" s="18" t="s">
         <v>62</v>
       </c>
@@ -8338,7 +8338,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A62" s="18" t="s">
         <v>62</v>
       </c>
@@ -8355,7 +8355,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A63" s="18" t="s">
         <v>62</v>
       </c>
@@ -8372,7 +8372,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A64" s="18" t="s">
         <v>62</v>
       </c>
@@ -8389,7 +8389,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A65" s="18" t="s">
         <v>62</v>
       </c>
@@ -8406,7 +8406,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A66" s="18" t="s">
         <v>62</v>
       </c>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="G66" s="2"/>
     </row>
-    <row r="67" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A67" s="18" t="s">
         <v>62</v>
       </c>
@@ -8442,7 +8442,7 @@
       </c>
       <c r="G67" s="2"/>
     </row>
-    <row r="68" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A68" s="18" t="s">
         <v>62</v>
       </c>
@@ -8459,7 +8459,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A69" s="18" t="s">
         <v>62</v>
       </c>
@@ -8476,7 +8476,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A70" s="18" t="s">
         <v>62</v>
       </c>
@@ -8493,7 +8493,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A71" s="18" t="s">
         <v>62</v>
       </c>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="G71" s="2"/>
     </row>
-    <row r="72" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A72" s="18" t="s">
         <v>62</v>
       </c>
@@ -8528,7 +8528,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A73" s="18" t="s">
         <v>62</v>
       </c>
@@ -8545,7 +8545,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A74" s="18" t="s">
         <v>62</v>
       </c>
@@ -8562,7 +8562,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A75" s="18" t="s">
         <v>62</v>
       </c>
@@ -8579,7 +8579,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A76" s="18" t="s">
         <v>62</v>
       </c>
@@ -8596,7 +8596,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A77" s="18" t="s">
         <v>62</v>
       </c>
@@ -8613,7 +8613,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A78" s="18" t="s">
         <v>62</v>
       </c>
@@ -8630,7 +8630,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A79" s="18" t="s">
         <v>62</v>
       </c>
@@ -8647,7 +8647,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A80" s="18" t="s">
         <v>62</v>
       </c>
@@ -8664,7 +8664,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A81" s="18" t="s">
         <v>62</v>
       </c>
@@ -8681,7 +8681,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A82" s="18" t="s">
         <v>62</v>
       </c>
@@ -8698,7 +8698,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A83" s="18" t="s">
         <v>62</v>
       </c>
@@ -8715,14 +8715,14 @@
         <v>226</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A84" s="18"/>
       <c r="B84" s="18"/>
       <c r="C84" s="14"/>
       <c r="D84" s="14"/>
       <c r="E84" s="18"/>
     </row>
-    <row r="85" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A85" s="18" t="s">
         <v>86</v>
       </c>
@@ -8739,7 +8739,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A86" s="18" t="s">
         <v>86</v>
       </c>
@@ -8756,7 +8756,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A87" s="18" t="s">
         <v>86</v>
       </c>
@@ -8773,7 +8773,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A88" s="18" t="s">
         <v>86</v>
       </c>
@@ -8790,7 +8790,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A89" s="18" t="s">
         <v>86</v>
       </c>
@@ -8807,7 +8807,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A90" s="18" t="s">
         <v>86</v>
       </c>
@@ -8824,7 +8824,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A91" s="18" t="s">
         <v>86</v>
       </c>
@@ -8841,14 +8841,14 @@
         <v>223</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A92" s="18"/>
       <c r="B92" s="18"/>
       <c r="C92" s="14"/>
       <c r="D92" s="14"/>
       <c r="E92" s="18"/>
     </row>
-    <row r="93" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A93" s="18" t="s">
         <v>94</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A94" s="18" t="s">
         <v>94</v>
       </c>
@@ -8882,7 +8882,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A95" s="18" t="s">
         <v>94</v>
       </c>
@@ -8899,7 +8899,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A96" s="18" t="s">
         <v>94</v>
       </c>
@@ -8916,7 +8916,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A97" s="18" t="s">
         <v>94</v>
       </c>
@@ -8933,7 +8933,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A98" s="18" t="s">
         <v>94</v>
       </c>
@@ -8950,7 +8950,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A99" s="18" t="s">
         <v>94</v>
       </c>
@@ -8967,7 +8967,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A100" s="18" t="s">
         <v>94</v>
       </c>
@@ -8984,7 +8984,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="101" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A101" s="18" t="s">
         <v>94</v>
       </c>
@@ -9001,7 +9001,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A102" s="18" t="s">
         <v>94</v>
       </c>
@@ -9018,14 +9018,14 @@
         <v>226</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A103" s="18"/>
       <c r="B103" s="18"/>
       <c r="C103" s="14"/>
       <c r="D103" s="14"/>
       <c r="E103" s="18"/>
     </row>
-    <row r="104" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A104" s="18" t="s">
         <v>103</v>
       </c>
@@ -9042,7 +9042,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A105" s="18" t="s">
         <v>103</v>
       </c>
@@ -9059,7 +9059,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A106" s="18" t="s">
         <v>103</v>
       </c>
@@ -9076,7 +9076,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A107" s="18" t="s">
         <v>103</v>
       </c>
@@ -9093,7 +9093,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A108" s="18" t="s">
         <v>103</v>
       </c>
@@ -9110,7 +9110,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A109" s="18" t="s">
         <v>103</v>
       </c>
@@ -9127,7 +9127,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A110" s="18" t="s">
         <v>103</v>
       </c>
@@ -9144,7 +9144,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A111" s="18" t="s">
         <v>103</v>
       </c>
@@ -9161,7 +9161,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A112" s="18" t="s">
         <v>103</v>
       </c>
@@ -9178,7 +9178,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A113" s="18" t="s">
         <v>103</v>
       </c>
@@ -9195,7 +9195,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A114" s="18" t="s">
         <v>103</v>
       </c>
@@ -9212,7 +9212,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A115" s="18" t="s">
         <v>103</v>
       </c>
@@ -9229,7 +9229,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A116" s="18" t="s">
         <v>103</v>
       </c>
@@ -9246,7 +9246,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A117" s="18" t="s">
         <v>103</v>
       </c>
@@ -9263,7 +9263,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A118" s="18" t="s">
         <v>103</v>
       </c>
@@ -9280,7 +9280,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A119" s="18" t="s">
         <v>103</v>
       </c>
@@ -9297,7 +9297,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A120" s="18" t="s">
         <v>103</v>
       </c>
@@ -9314,7 +9314,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A121" s="18" t="s">
         <v>103</v>
       </c>
@@ -9331,14 +9331,14 @@
         <v>226</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A122" s="18"/>
       <c r="B122" s="18"/>
       <c r="C122" s="14"/>
       <c r="D122" s="14"/>
       <c r="E122" s="18"/>
     </row>
-    <row r="123" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A123" s="18" t="s">
         <v>166</v>
       </c>
@@ -9355,7 +9355,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A124" s="18" t="s">
         <v>166</v>
       </c>
@@ -9372,7 +9372,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A125" s="18" t="s">
         <v>166</v>
       </c>
@@ -9389,7 +9389,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A126" s="18" t="s">
         <v>166</v>
       </c>
@@ -9406,7 +9406,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A127" s="18" t="s">
         <v>166</v>
       </c>
@@ -9423,7 +9423,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A128" s="18" t="s">
         <v>166</v>
       </c>
@@ -9440,7 +9440,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A129" s="18" t="s">
         <v>166</v>
       </c>
@@ -9457,7 +9457,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A130" s="18" t="s">
         <v>166</v>
       </c>
@@ -9474,7 +9474,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A131" s="18" t="s">
         <v>166</v>
       </c>
@@ -9491,7 +9491,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A132" s="18" t="s">
         <v>166</v>
       </c>
@@ -9508,7 +9508,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A133" s="18" t="s">
         <v>166</v>
       </c>
@@ -9525,7 +9525,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A134" s="18" t="s">
         <v>166</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A135" s="18" t="s">
         <v>166</v>
       </c>
@@ -9559,7 +9559,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A136" s="18" t="s">
         <v>166</v>
       </c>
@@ -9576,7 +9576,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A137" s="18" t="s">
         <v>166</v>
       </c>
@@ -9593,7 +9593,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A138" s="18" t="s">
         <v>166</v>
       </c>
@@ -9610,7 +9610,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A139" s="18" t="s">
         <v>166</v>
       </c>
@@ -9627,7 +9627,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A140" s="18" t="s">
         <v>166</v>
       </c>
@@ -9644,7 +9644,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A141" s="18" t="s">
         <v>166</v>
       </c>
@@ -9661,7 +9661,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A142" s="18" t="s">
         <v>166</v>
       </c>
@@ -9678,7 +9678,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A143" s="18" t="s">
         <v>166</v>
       </c>
@@ -9695,7 +9695,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A144" s="18" t="s">
         <v>166</v>
       </c>
@@ -9712,7 +9712,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A145" s="18" t="s">
         <v>166</v>
       </c>
@@ -9729,7 +9729,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A146" s="18" t="s">
         <v>166</v>
       </c>
@@ -9746,7 +9746,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A147" s="18" t="s">
         <v>166</v>
       </c>
@@ -9763,7 +9763,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A148" s="18" t="s">
         <v>166</v>
       </c>
@@ -9780,7 +9780,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A149" s="18" t="s">
         <v>166</v>
       </c>
@@ -9797,7 +9797,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A150" s="18" t="s">
         <v>166</v>
       </c>
@@ -9814,7 +9814,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A151" s="18" t="s">
         <v>166</v>
       </c>
@@ -9831,14 +9831,14 @@
         <v>240</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A152" s="18"/>
       <c r="B152" s="18"/>
       <c r="C152" s="14"/>
       <c r="D152" s="14"/>
       <c r="E152" s="18"/>
     </row>
-    <row r="153" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A153" s="18" t="s">
         <v>196</v>
       </c>
@@ -9855,7 +9855,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A154" s="18" t="s">
         <v>196</v>
       </c>
@@ -9872,7 +9872,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A155" s="18" t="s">
         <v>196</v>
       </c>
@@ -9889,7 +9889,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A156" s="18" t="s">
         <v>196</v>
       </c>
@@ -9906,7 +9906,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A157" s="18" t="s">
         <v>196</v>
       </c>
@@ -9923,7 +9923,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A158" s="18" t="s">
         <v>196</v>
       </c>
@@ -9940,7 +9940,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A159" s="18" t="s">
         <v>196</v>
       </c>
@@ -9957,7 +9957,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A160" s="18" t="s">
         <v>196</v>
       </c>
@@ -9974,7 +9974,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A161" s="18" t="s">
         <v>196</v>
       </c>
@@ -9991,7 +9991,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A162" s="18" t="s">
         <v>196</v>
       </c>
@@ -10008,7 +10008,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A163" s="18" t="s">
         <v>196</v>
       </c>
@@ -10025,7 +10025,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A164" s="18" t="s">
         <v>196</v>
       </c>
@@ -10042,7 +10042,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A165" s="18" t="s">
         <v>196</v>
       </c>
@@ -10059,7 +10059,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A166" s="18" t="s">
         <v>196</v>
       </c>
@@ -10076,7 +10076,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A167" s="18" t="s">
         <v>196</v>
       </c>
@@ -10093,7 +10093,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="171" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A171" s="18" t="s">
         <v>212</v>
       </c>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="D171" s="14"/>
     </row>
-    <row r="172" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A172" s="18" t="s">
         <v>212</v>
       </c>
@@ -10117,7 +10117,7 @@
       </c>
       <c r="D172" s="14"/>
     </row>
-    <row r="173" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A173" s="18" t="s">
         <v>212</v>
       </c>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="D173" s="14"/>
     </row>
-    <row r="174" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A174" s="18" t="s">
         <v>212</v>
       </c>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="D174" s="14"/>
     </row>
-    <row r="175" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A175" s="18" t="s">
         <v>212</v>
       </c>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="D175" s="14"/>
     </row>
-    <row r="176" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A176" s="18" t="s">
         <v>212</v>
       </c>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="D176" s="14"/>
     </row>
-    <row r="177" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A177" s="18" t="s">
         <v>212</v>
       </c>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="D177" s="14"/>
     </row>
-    <row r="178" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A178" s="18" t="s">
         <v>212</v>
       </c>
@@ -10189,7 +10189,7 @@
       </c>
       <c r="D178" s="14"/>
     </row>
-    <row r="179" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A179" s="18" t="s">
         <v>212</v>
       </c>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="D179" s="14"/>
     </row>
-    <row r="181" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="18" t="s">
         <v>120</v>
       </c>
@@ -10213,7 +10213,7 @@
       </c>
       <c r="D181" s="14"/>
     </row>
-    <row r="182" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="18" t="s">
         <v>120</v>
       </c>
@@ -10225,7 +10225,7 @@
       </c>
       <c r="D182" s="14"/>
     </row>
-    <row r="183" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="18" t="s">
         <v>120</v>
       </c>
@@ -10237,7 +10237,7 @@
       </c>
       <c r="D183" s="14"/>
     </row>
-    <row r="184" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="18" t="s">
         <v>120</v>
       </c>
@@ -10249,7 +10249,7 @@
       </c>
       <c r="D184" s="14"/>
     </row>
-    <row r="185" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="18" t="s">
         <v>120</v>
       </c>
@@ -10261,7 +10261,7 @@
       </c>
       <c r="D185" s="14"/>
     </row>
-    <row r="186" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="18" t="s">
         <v>120</v>
       </c>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="D186" s="14"/>
     </row>
-    <row r="187" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="18" t="s">
         <v>120</v>
       </c>
@@ -10285,7 +10285,7 @@
       </c>
       <c r="D187" s="14"/>
     </row>
-    <row r="188" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="18" t="s">
         <v>120</v>
       </c>
@@ -10297,13 +10297,13 @@
       </c>
       <c r="D188" s="14"/>
     </row>
-    <row r="189" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="18"/>
       <c r="B189" s="18"/>
       <c r="C189" s="14"/>
       <c r="D189" s="14"/>
     </row>
-    <row r="190" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="18" t="s">
         <v>129</v>
       </c>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="D190" s="14"/>
     </row>
-    <row r="191" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="18" t="s">
         <v>129</v>
       </c>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="D191" s="14"/>
     </row>
-    <row r="192" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="18" t="s">
         <v>129</v>
       </c>
@@ -10339,7 +10339,7 @@
       </c>
       <c r="D192" s="14"/>
     </row>
-    <row r="193" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="18" t="s">
         <v>129</v>
       </c>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="D193" s="14"/>
     </row>
-    <row r="194" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="18" t="s">
         <v>129</v>
       </c>
@@ -10363,7 +10363,7 @@
       </c>
       <c r="D194" s="14"/>
     </row>
-    <row r="195" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="18" t="s">
         <v>129</v>
       </c>
@@ -10375,7 +10375,7 @@
       </c>
       <c r="D195" s="14"/>
     </row>
-    <row r="196" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="18" t="s">
         <v>129</v>
       </c>
@@ -10387,7 +10387,7 @@
       </c>
       <c r="D196" s="14"/>
     </row>
-    <row r="197" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="18" t="s">
         <v>129</v>
       </c>
@@ -10399,7 +10399,7 @@
       </c>
       <c r="D197" s="14"/>
     </row>
-    <row r="198" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="18" t="s">
         <v>129</v>
       </c>
@@ -10411,7 +10411,7 @@
       </c>
       <c r="D198" s="14"/>
     </row>
-    <row r="199" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="18" t="s">
         <v>129</v>
       </c>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="D199" s="14"/>
     </row>
-    <row r="200" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="18" t="s">
         <v>129</v>
       </c>
@@ -10435,7 +10435,7 @@
       </c>
       <c r="D200" s="14"/>
     </row>
-    <row r="201" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="18" t="s">
         <v>129</v>
       </c>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="D201" s="14"/>
     </row>
-    <row r="202" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="18" t="s">
         <v>129</v>
       </c>
@@ -10459,7 +10459,7 @@
       </c>
       <c r="D202" s="14"/>
     </row>
-    <row r="203" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="18" t="s">
         <v>129</v>
       </c>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="D203" s="14"/>
     </row>
-    <row r="204" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="18" t="s">
         <v>129</v>
       </c>
@@ -10483,13 +10483,13 @@
       </c>
       <c r="D204" s="14"/>
     </row>
-    <row r="205" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="18"/>
       <c r="B205" s="18"/>
       <c r="C205" s="14"/>
       <c r="D205" s="14"/>
     </row>
-    <row r="206" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="18" t="s">
         <v>145</v>
       </c>
@@ -10501,7 +10501,7 @@
       </c>
       <c r="D206" s="14"/>
     </row>
-    <row r="207" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="18" t="s">
         <v>145</v>
       </c>
@@ -10513,13 +10513,13 @@
       </c>
       <c r="D207" s="14"/>
     </row>
-    <row r="208" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="18"/>
       <c r="B208" s="18"/>
       <c r="C208" s="14"/>
       <c r="D208" s="14"/>
     </row>
-    <row r="209" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="18" t="s">
         <v>148</v>
       </c>
@@ -10531,7 +10531,7 @@
       </c>
       <c r="D209" s="14"/>
     </row>
-    <row r="210" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="18" t="s">
         <v>148</v>
       </c>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="D210" s="14"/>
     </row>
-    <row r="211" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="18" t="s">
         <v>148</v>
       </c>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="D211" s="14"/>
     </row>
-    <row r="212" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="18" t="s">
         <v>148</v>
       </c>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="D212" s="14"/>
     </row>
-    <row r="213" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="18" t="s">
         <v>148</v>
       </c>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="D213" s="14"/>
     </row>
-    <row r="214" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="18" t="s">
         <v>148</v>
       </c>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="D214" s="14"/>
     </row>
-    <row r="215" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="18" t="s">
         <v>148</v>
       </c>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="D215" s="14"/>
     </row>
-    <row r="216" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="18" t="s">
         <v>148</v>
       </c>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="D216" s="14"/>
     </row>
-    <row r="217" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="18" t="s">
         <v>148</v>
       </c>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="D217" s="14"/>
     </row>
-    <row r="218" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="18" t="s">
         <v>148</v>
       </c>
@@ -10639,7 +10639,7 @@
       </c>
       <c r="D218" s="14"/>
     </row>
-    <row r="219" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="18" t="s">
         <v>148</v>
       </c>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="D219" s="14"/>
     </row>
-    <row r="220" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="18" t="s">
         <v>148</v>
       </c>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="D220" s="14"/>
     </row>
-    <row r="221" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="18" t="s">
         <v>148</v>
       </c>
@@ -10675,7 +10675,7 @@
       </c>
       <c r="D221" s="14"/>
     </row>
-    <row r="222" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="18" t="s">
         <v>148</v>
       </c>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="D222" s="14"/>
     </row>
-    <row r="223" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="18" t="s">
         <v>148</v>
       </c>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="D223" s="14"/>
     </row>
-    <row r="224" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="18" t="s">
         <v>148</v>
       </c>
@@ -10711,7 +10711,7 @@
       </c>
       <c r="D224" s="14"/>
     </row>
-    <row r="225" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="18" t="s">
         <v>148</v>
       </c>
@@ -10734,16 +10734,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:G229"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" style="20" customWidth="1"/>
-    <col min="2" max="2" width="5.42578125" style="20" customWidth="1"/>
-    <col min="3" max="3" width="110.42578125" style="21" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" style="21" customWidth="1"/>
-    <col min="5" max="5" width="31.42578125" style="20" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" style="20" customWidth="1"/>
+    <col min="2" max="2" width="5.44140625" style="20" customWidth="1"/>
+    <col min="3" max="3" width="110.44140625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="31.44140625" style="20" customWidth="1"/>
     <col min="6" max="6" width="31" customWidth="1"/>
-    <col min="7" max="7" width="9.140625"/>
-    <col min="8" max="8" width="42.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.109375"/>
+    <col min="8" max="8" width="42.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10763,7 +10763,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>3</v>
       </c>
@@ -10779,11 +10779,11 @@
       <c r="E2" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="38" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>3</v>
       </c>
@@ -10799,9 +10799,9 @@
       <c r="E3" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="F3" s="36"/>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F3" s="38"/>
+    </row>
+    <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>3</v>
       </c>
@@ -10821,7 +10821,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>3</v>
       </c>
@@ -10841,7 +10841,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
         <v>3</v>
       </c>
@@ -10857,11 +10857,11 @@
       <c r="E6" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="34" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>3</v>
       </c>
@@ -10877,9 +10877,9 @@
       <c r="E7" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="F7" s="34"/>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F7" s="35"/>
+    </row>
+    <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>3</v>
       </c>
@@ -10899,7 +10899,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>3</v>
       </c>
@@ -10919,7 +10919,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
         <v>3</v>
       </c>
@@ -10939,7 +10939,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>3</v>
       </c>
@@ -10959,7 +10959,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
         <v>3</v>
       </c>
@@ -10975,11 +10975,11 @@
       <c r="E12" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="F12" s="38" t="s">
+      <c r="F12" s="39" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>3</v>
       </c>
@@ -10995,9 +10995,9 @@
       <c r="E13" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="F13" s="39"/>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F13" s="40"/>
+    </row>
+    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
         <v>3</v>
       </c>
@@ -11017,7 +11017,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>3</v>
       </c>
@@ -11037,7 +11037,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>3</v>
       </c>
@@ -11053,11 +11053,11 @@
       <c r="E16" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F16" s="37" t="s">
+      <c r="F16" s="34" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>3</v>
       </c>
@@ -11073,16 +11073,16 @@
       <c r="E17" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F17" s="34"/>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F17" s="35"/>
+    </row>
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="18"/>
       <c r="B18" s="18"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
       <c r="E18" s="18"/>
     </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
         <v>20</v>
       </c>
@@ -11098,11 +11098,11 @@
       <c r="E19" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="F19" s="37" t="s">
+      <c r="F19" s="34" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="18" t="s">
         <v>20</v>
       </c>
@@ -11118,9 +11118,9 @@
       <c r="E20" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="F20" s="34"/>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F20" s="35"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
         <v>20</v>
       </c>
@@ -11136,9 +11136,9 @@
       <c r="E21" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="F21" s="34"/>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F21" s="35"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
         <v>20</v>
       </c>
@@ -11158,7 +11158,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
         <v>20</v>
       </c>
@@ -11178,7 +11178,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
         <v>20</v>
       </c>
@@ -11194,11 +11194,11 @@
       <c r="E24" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="F24" s="37" t="s">
+      <c r="F24" s="34" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
         <v>20</v>
       </c>
@@ -11214,9 +11214,9 @@
       <c r="E25" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="F25" s="34"/>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F25" s="35"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
         <v>20</v>
       </c>
@@ -11232,9 +11232,9 @@
       <c r="E26" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="F26" s="34"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F26" s="35"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="18" t="s">
         <v>20</v>
       </c>
@@ -11250,11 +11250,11 @@
       <c r="E27" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F27" s="40" t="s">
+      <c r="F27" s="36" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="18" t="s">
         <v>20</v>
       </c>
@@ -11270,9 +11270,9 @@
       <c r="E28" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F28" s="41"/>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F28" s="37"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="18" t="s">
         <v>20</v>
       </c>
@@ -11288,9 +11288,9 @@
       <c r="E29" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F29" s="41"/>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F29" s="37"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="18" t="s">
         <v>20</v>
       </c>
@@ -11306,9 +11306,9 @@
       <c r="E30" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F30" s="41"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F30" s="37"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="18" t="s">
         <v>20</v>
       </c>
@@ -11324,11 +11324,11 @@
       <c r="E31" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="F31" s="37" t="s">
+      <c r="F31" s="34" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
         <v>20</v>
       </c>
@@ -11344,9 +11344,9 @@
       <c r="E32" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="F32" s="34"/>
-    </row>
-    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F32" s="35"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="18" t="s">
         <v>20</v>
       </c>
@@ -11362,9 +11362,9 @@
       <c r="E33" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="F33" s="34"/>
-    </row>
-    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F33" s="35"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
         <v>20</v>
       </c>
@@ -11380,16 +11380,16 @@
       <c r="E34" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="F34" s="34"/>
-    </row>
-    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F34" s="35"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="18"/>
       <c r="B35" s="18"/>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>
       <c r="E35" s="18"/>
     </row>
-    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="18" t="s">
         <v>37</v>
       </c>
@@ -11406,7 +11406,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="18" t="s">
         <v>39</v>
       </c>
@@ -11423,7 +11423,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="18" t="s">
         <v>39</v>
       </c>
@@ -11440,7 +11440,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="18" t="s">
         <v>39</v>
       </c>
@@ -11457,7 +11457,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="18" t="s">
         <v>37</v>
       </c>
@@ -11473,11 +11473,11 @@
       <c r="E40" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="F40" s="37" t="s">
+      <c r="F40" s="34" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="18" t="s">
         <v>37</v>
       </c>
@@ -11493,9 +11493,9 @@
       <c r="E41" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="F41" s="34"/>
-    </row>
-    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F41" s="35"/>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="s">
         <v>37</v>
       </c>
@@ -11512,7 +11512,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A43" s="18" t="s">
         <v>37</v>
       </c>
@@ -11528,11 +11528,11 @@
       <c r="E43" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="F43" s="37" t="s">
+      <c r="F43" s="34" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A44" s="18" t="s">
         <v>37</v>
       </c>
@@ -11548,9 +11548,9 @@
       <c r="E44" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="F44" s="34"/>
-    </row>
-    <row r="45" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="F44" s="35"/>
+    </row>
+    <row r="45" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A45" s="18" t="s">
         <v>37</v>
       </c>
@@ -11567,7 +11567,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A46" s="18" t="s">
         <v>39</v>
       </c>
@@ -11584,7 +11584,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A47" s="18" t="s">
         <v>37</v>
       </c>
@@ -11601,7 +11601,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
         <v>39</v>
       </c>
@@ -11618,7 +11618,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A49" s="18" t="s">
         <v>37</v>
       </c>
@@ -11635,7 +11635,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A50" s="18" t="s">
         <v>39</v>
       </c>
@@ -11651,11 +11651,11 @@
       <c r="E50" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F50" s="34" t="s">
+      <c r="F50" s="35" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A51" s="18" t="s">
         <v>39</v>
       </c>
@@ -11671,9 +11671,9 @@
       <c r="E51" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F51" s="34"/>
-    </row>
-    <row r="52" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="F51" s="35"/>
+    </row>
+    <row r="52" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A52" s="18" t="s">
         <v>39</v>
       </c>
@@ -11690,7 +11690,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A53" s="18" t="s">
         <v>39</v>
       </c>
@@ -11707,7 +11707,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A54" s="18" t="s">
         <v>39</v>
       </c>
@@ -11724,7 +11724,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A55" s="18" t="s">
         <v>37</v>
       </c>
@@ -11741,7 +11741,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A56" s="18" t="s">
         <v>39</v>
       </c>
@@ -11758,7 +11758,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A57" s="18" t="s">
         <v>39</v>
       </c>
@@ -11775,7 +11775,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A58" s="18" t="s">
         <v>37</v>
       </c>
@@ -11792,21 +11792,21 @@
         <v>226</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A59" s="18"/>
       <c r="B59" s="18"/>
       <c r="C59" s="14"/>
       <c r="D59" s="14"/>
       <c r="E59" s="18"/>
     </row>
-    <row r="60" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A60" s="18"/>
       <c r="B60" s="18"/>
       <c r="C60" s="14"/>
       <c r="D60" s="14"/>
       <c r="E60" s="18"/>
     </row>
-    <row r="61" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A61" s="18" t="s">
         <v>62</v>
       </c>
@@ -11823,7 +11823,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A62" s="18" t="s">
         <v>62</v>
       </c>
@@ -11840,7 +11840,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A63" s="18" t="s">
         <v>62</v>
       </c>
@@ -11857,7 +11857,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A64" s="18" t="s">
         <v>62</v>
       </c>
@@ -11874,7 +11874,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A65" s="18" t="s">
         <v>62</v>
       </c>
@@ -11891,7 +11891,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A66" s="18" t="s">
         <v>62</v>
       </c>
@@ -11909,7 +11909,7 @@
       </c>
       <c r="G66" s="2"/>
     </row>
-    <row r="67" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A67" s="18" t="s">
         <v>62</v>
       </c>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="G67" s="2"/>
     </row>
-    <row r="68" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A68" s="18" t="s">
         <v>62</v>
       </c>
@@ -11944,7 +11944,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A69" s="18" t="s">
         <v>62</v>
       </c>
@@ -11961,7 +11961,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A70" s="18" t="s">
         <v>62</v>
       </c>
@@ -11978,7 +11978,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A71" s="18" t="s">
         <v>62</v>
       </c>
@@ -11996,7 +11996,7 @@
       </c>
       <c r="G71" s="2"/>
     </row>
-    <row r="72" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A72" s="18" t="s">
         <v>62</v>
       </c>
@@ -12013,7 +12013,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A73" s="18" t="s">
         <v>62</v>
       </c>
@@ -12030,7 +12030,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A74" s="18" t="s">
         <v>62</v>
       </c>
@@ -12047,7 +12047,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A75" s="18" t="s">
         <v>62</v>
       </c>
@@ -12064,7 +12064,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A76" s="18" t="s">
         <v>62</v>
       </c>
@@ -12081,7 +12081,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A77" s="18" t="s">
         <v>62</v>
       </c>
@@ -12098,7 +12098,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A78" s="18" t="s">
         <v>62</v>
       </c>
@@ -12115,7 +12115,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A79" s="18" t="s">
         <v>62</v>
       </c>
@@ -12132,7 +12132,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A80" s="18" t="s">
         <v>62</v>
       </c>
@@ -12149,7 +12149,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A81" s="18" t="s">
         <v>62</v>
       </c>
@@ -12166,7 +12166,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A82" s="18" t="s">
         <v>62</v>
       </c>
@@ -12183,7 +12183,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A83" s="18" t="s">
         <v>62</v>
       </c>
@@ -12200,14 +12200,14 @@
         <v>226</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A84" s="18"/>
       <c r="B84" s="18"/>
       <c r="C84" s="14"/>
       <c r="D84" s="14"/>
       <c r="E84" s="18"/>
     </row>
-    <row r="85" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A85" s="18" t="s">
         <v>86</v>
       </c>
@@ -12227,7 +12227,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A86" s="18" t="s">
         <v>86</v>
       </c>
@@ -12243,11 +12243,11 @@
       <c r="E86" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="F86" s="34" t="s">
+      <c r="F86" s="35" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="18" t="s">
         <v>86</v>
       </c>
@@ -12263,9 +12263,9 @@
       <c r="E87" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="F87" s="34"/>
-    </row>
-    <row r="88" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F87" s="35"/>
+    </row>
+    <row r="88" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="18" t="s">
         <v>86</v>
       </c>
@@ -12281,11 +12281,11 @@
       <c r="E88" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="F88" s="35" t="s">
+      <c r="F88" s="41" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A89" s="18" t="s">
         <v>86</v>
       </c>
@@ -12301,9 +12301,9 @@
       <c r="E89" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="F89" s="35"/>
-    </row>
-    <row r="90" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="F89" s="41"/>
+    </row>
+    <row r="90" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A90" s="18" t="s">
         <v>86</v>
       </c>
@@ -12319,9 +12319,9 @@
       <c r="E90" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="F90" s="35"/>
-    </row>
-    <row r="91" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="F90" s="41"/>
+    </row>
+    <row r="91" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A91" s="18" t="s">
         <v>86</v>
       </c>
@@ -12341,14 +12341,14 @@
         <v>308</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A92" s="18"/>
       <c r="B92" s="18"/>
       <c r="C92" s="14"/>
       <c r="D92" s="14"/>
       <c r="E92" s="18"/>
     </row>
-    <row r="93" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A93" s="18" t="s">
         <v>94</v>
       </c>
@@ -12365,7 +12365,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A94" s="18" t="s">
         <v>94</v>
       </c>
@@ -12382,7 +12382,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A95" s="18" t="s">
         <v>94</v>
       </c>
@@ -12399,7 +12399,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A96" s="18" t="s">
         <v>94</v>
       </c>
@@ -12416,7 +12416,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A97" s="18" t="s">
         <v>94</v>
       </c>
@@ -12433,7 +12433,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A98" s="18" t="s">
         <v>94</v>
       </c>
@@ -12450,7 +12450,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A99" s="18" t="s">
         <v>94</v>
       </c>
@@ -12466,11 +12466,11 @@
       <c r="E99" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="F99" s="34" t="s">
+      <c r="F99" s="35" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A100" s="18" t="s">
         <v>94</v>
       </c>
@@ -12486,9 +12486,9 @@
       <c r="E100" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="F100" s="34"/>
-    </row>
-    <row r="101" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="F100" s="35"/>
+    </row>
+    <row r="101" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A101" s="18" t="s">
         <v>94</v>
       </c>
@@ -12508,7 +12508,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A102" s="18" t="s">
         <v>94</v>
       </c>
@@ -12528,14 +12528,14 @@
         <v>310</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A103" s="18"/>
       <c r="B103" s="18"/>
       <c r="C103" s="14"/>
       <c r="D103" s="14"/>
       <c r="E103" s="18"/>
     </row>
-    <row r="104" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A104" s="18" t="s">
         <v>103</v>
       </c>
@@ -12552,7 +12552,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A105" s="18" t="s">
         <v>103</v>
       </c>
@@ -12569,7 +12569,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A106" s="18" t="s">
         <v>103</v>
       </c>
@@ -12585,11 +12585,11 @@
       <c r="E106" s="18" t="s">
         <v>237</v>
       </c>
-      <c r="F106" s="34" t="s">
+      <c r="F106" s="35" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A107" s="18" t="s">
         <v>103</v>
       </c>
@@ -12605,9 +12605,9 @@
       <c r="E107" s="18" t="s">
         <v>237</v>
       </c>
-      <c r="F107" s="34"/>
-    </row>
-    <row r="108" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="F107" s="35"/>
+    </row>
+    <row r="108" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A108" s="18" t="s">
         <v>103</v>
       </c>
@@ -12624,7 +12624,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A109" s="18" t="s">
         <v>103</v>
       </c>
@@ -12641,7 +12641,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A110" s="18" t="s">
         <v>103</v>
       </c>
@@ -12658,7 +12658,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A111" s="18" t="s">
         <v>103</v>
       </c>
@@ -12675,7 +12675,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A112" s="18" t="s">
         <v>103</v>
       </c>
@@ -12692,7 +12692,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A113" s="18" t="s">
         <v>103</v>
       </c>
@@ -12709,7 +12709,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A114" s="18" t="s">
         <v>103</v>
       </c>
@@ -12725,11 +12725,11 @@
       <c r="E114" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="F114" s="34" t="s">
+      <c r="F114" s="35" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A115" s="18" t="s">
         <v>103</v>
       </c>
@@ -12745,9 +12745,9 @@
       <c r="E115" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="F115" s="34"/>
-    </row>
-    <row r="116" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="F115" s="35"/>
+    </row>
+    <row r="116" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A116" s="18" t="s">
         <v>103</v>
       </c>
@@ -12767,7 +12767,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A117" s="18" t="s">
         <v>103</v>
       </c>
@@ -12784,7 +12784,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A118" s="18" t="s">
         <v>103</v>
       </c>
@@ -12800,11 +12800,11 @@
       <c r="E118" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="F118" s="34" t="s">
+      <c r="F118" s="35" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A119" s="18" t="s">
         <v>103</v>
       </c>
@@ -12820,9 +12820,9 @@
       <c r="E119" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="F119" s="34"/>
-    </row>
-    <row r="120" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="F119" s="35"/>
+    </row>
+    <row r="120" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A120" s="18" t="s">
         <v>103</v>
       </c>
@@ -12842,7 +12842,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A121" s="18" t="s">
         <v>103</v>
       </c>
@@ -12862,14 +12862,14 @@
         <v>314</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A122" s="18"/>
       <c r="B122" s="18"/>
       <c r="C122" s="14"/>
       <c r="D122" s="14"/>
       <c r="E122" s="18"/>
     </row>
-    <row r="123" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A123" s="18" t="s">
         <v>166</v>
       </c>
@@ -12886,7 +12886,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A124" s="18" t="s">
         <v>166</v>
       </c>
@@ -12903,7 +12903,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A125" s="18" t="s">
         <v>166</v>
       </c>
@@ -12920,7 +12920,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A126" s="18" t="s">
         <v>166</v>
       </c>
@@ -12937,7 +12937,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A127" s="18" t="s">
         <v>166</v>
       </c>
@@ -12954,7 +12954,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A128" s="18" t="s">
         <v>166</v>
       </c>
@@ -12971,7 +12971,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="129" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A129" s="18" t="s">
         <v>166</v>
       </c>
@@ -12988,7 +12988,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="130" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A130" s="18" t="s">
         <v>166</v>
       </c>
@@ -13005,7 +13005,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="131" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A131" s="18" t="s">
         <v>166</v>
       </c>
@@ -13022,7 +13022,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A132" s="18" t="s">
         <v>166</v>
       </c>
@@ -13039,7 +13039,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A133" s="18" t="s">
         <v>166</v>
       </c>
@@ -13056,7 +13056,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A134" s="18" t="s">
         <v>166</v>
       </c>
@@ -13073,7 +13073,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A135" s="18" t="s">
         <v>166</v>
       </c>
@@ -13090,7 +13090,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A136" s="18" t="s">
         <v>166</v>
       </c>
@@ -13107,7 +13107,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A137" s="18" t="s">
         <v>166</v>
       </c>
@@ -13124,7 +13124,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A138" s="18" t="s">
         <v>166</v>
       </c>
@@ -13141,7 +13141,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A139" s="18" t="s">
         <v>166</v>
       </c>
@@ -13158,7 +13158,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A140" s="18" t="s">
         <v>166</v>
       </c>
@@ -13175,7 +13175,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A141" s="18" t="s">
         <v>166</v>
       </c>
@@ -13192,7 +13192,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A142" s="18" t="s">
         <v>166</v>
       </c>
@@ -13209,7 +13209,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A143" s="18" t="s">
         <v>166</v>
       </c>
@@ -13226,7 +13226,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A144" s="18" t="s">
         <v>166</v>
       </c>
@@ -13243,7 +13243,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="145" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A145" s="18" t="s">
         <v>166</v>
       </c>
@@ -13260,7 +13260,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="146" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A146" s="18" t="s">
         <v>166</v>
       </c>
@@ -13277,7 +13277,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A147" s="18" t="s">
         <v>166</v>
       </c>
@@ -13294,7 +13294,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A148" s="18" t="s">
         <v>166</v>
       </c>
@@ -13311,7 +13311,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="149" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A149" s="18" t="s">
         <v>166</v>
       </c>
@@ -13328,7 +13328,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="150" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A150" s="18" t="s">
         <v>166</v>
       </c>
@@ -13345,7 +13345,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="151" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A151" s="18" t="s">
         <v>166</v>
       </c>
@@ -13362,14 +13362,14 @@
         <v>240</v>
       </c>
     </row>
-    <row r="152" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A152" s="18"/>
       <c r="B152" s="18"/>
       <c r="C152" s="14"/>
       <c r="D152" s="14"/>
       <c r="E152" s="18"/>
     </row>
-    <row r="153" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A153" s="18" t="s">
         <v>196</v>
       </c>
@@ -13385,11 +13385,11 @@
       <c r="E153" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="F153" s="34" t="s">
+      <c r="F153" s="35" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A154" s="18" t="s">
         <v>196</v>
       </c>
@@ -13405,9 +13405,9 @@
       <c r="E154" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="F154" s="34"/>
-    </row>
-    <row r="155" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="F154" s="35"/>
+    </row>
+    <row r="155" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A155" s="18" t="s">
         <v>196</v>
       </c>
@@ -13427,7 +13427,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="156" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A156" s="18" t="s">
         <v>196</v>
       </c>
@@ -13443,11 +13443,11 @@
       <c r="E156" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="F156" s="34" t="s">
+      <c r="F156" s="35" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="157" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A157" s="18" t="s">
         <v>196</v>
       </c>
@@ -13463,9 +13463,9 @@
       <c r="E157" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="F157" s="34"/>
-    </row>
-    <row r="158" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="F157" s="35"/>
+    </row>
+    <row r="158" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A158" s="18" t="s">
         <v>196</v>
       </c>
@@ -13481,11 +13481,11 @@
       <c r="E158" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="F158" s="34" t="s">
+      <c r="F158" s="35" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A159" s="18" t="s">
         <v>196</v>
       </c>
@@ -13501,9 +13501,9 @@
       <c r="E159" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="F159" s="34"/>
-    </row>
-    <row r="160" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="F159" s="35"/>
+    </row>
+    <row r="160" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A160" s="18" t="s">
         <v>196</v>
       </c>
@@ -13523,7 +13523,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="161" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A161" s="18" t="s">
         <v>196</v>
       </c>
@@ -13539,11 +13539,11 @@
       <c r="E161" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="F161" s="34" t="s">
+      <c r="F161" s="35" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="162" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A162" s="18" t="s">
         <v>196</v>
       </c>
@@ -13559,9 +13559,9 @@
       <c r="E162" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="F162" s="34"/>
-    </row>
-    <row r="163" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="F162" s="35"/>
+    </row>
+    <row r="163" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A163" s="18" t="s">
         <v>196</v>
       </c>
@@ -13577,11 +13577,11 @@
       <c r="E163" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F163" s="34" t="s">
+      <c r="F163" s="35" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="164" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A164" s="18" t="s">
         <v>196</v>
       </c>
@@ -13597,9 +13597,9 @@
       <c r="E164" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F164" s="34"/>
-    </row>
-    <row r="165" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="F164" s="35"/>
+    </row>
+    <row r="165" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A165" s="18" t="s">
         <v>196</v>
       </c>
@@ -13615,9 +13615,9 @@
       <c r="E165" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F165" s="34"/>
-    </row>
-    <row r="166" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="F165" s="35"/>
+    </row>
+    <row r="166" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A166" s="18" t="s">
         <v>196</v>
       </c>
@@ -13637,7 +13637,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A167" s="18" t="s">
         <v>196</v>
       </c>
@@ -13657,7 +13657,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="169" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="20" t="s">
         <v>435</v>
       </c>
@@ -13674,7 +13674,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="170" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="20" t="s">
         <v>435</v>
       </c>
@@ -13691,7 +13691,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="171" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="20" t="s">
         <v>435</v>
       </c>
@@ -13708,7 +13708,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="172" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="20" t="s">
         <v>435</v>
       </c>
@@ -13725,7 +13725,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="173" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="20" t="s">
         <v>435</v>
       </c>
@@ -13742,7 +13742,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="175" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A175" s="18" t="s">
         <v>212</v>
       </c>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="D175" s="14"/>
     </row>
-    <row r="176" spans="1:6" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:6" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A176" s="18" t="s">
         <v>212</v>
       </c>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="D176" s="14"/>
     </row>
-    <row r="177" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A177" s="18" t="s">
         <v>212</v>
       </c>
@@ -13778,7 +13778,7 @@
       </c>
       <c r="D177" s="14"/>
     </row>
-    <row r="178" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A178" s="18" t="s">
         <v>212</v>
       </c>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="D178" s="14"/>
     </row>
-    <row r="179" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A179" s="18" t="s">
         <v>212</v>
       </c>
@@ -13802,7 +13802,7 @@
       </c>
       <c r="D179" s="14"/>
     </row>
-    <row r="180" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A180" s="18" t="s">
         <v>212</v>
       </c>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="D180" s="14"/>
     </row>
-    <row r="181" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A181" s="18" t="s">
         <v>212</v>
       </c>
@@ -13826,7 +13826,7 @@
       </c>
       <c r="D181" s="14"/>
     </row>
-    <row r="182" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A182" s="18" t="s">
         <v>212</v>
       </c>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="D182" s="14"/>
     </row>
-    <row r="183" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A183" s="18" t="s">
         <v>212</v>
       </c>
@@ -13850,7 +13850,7 @@
       </c>
       <c r="D183" s="14"/>
     </row>
-    <row r="185" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="18" t="s">
         <v>120</v>
       </c>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="D185" s="14"/>
     </row>
-    <row r="186" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="18" t="s">
         <v>120</v>
       </c>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="D186" s="14"/>
     </row>
-    <row r="187" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="18" t="s">
         <v>120</v>
       </c>
@@ -13886,7 +13886,7 @@
       </c>
       <c r="D187" s="14"/>
     </row>
-    <row r="188" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="18" t="s">
         <v>120</v>
       </c>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="D188" s="14"/>
     </row>
-    <row r="189" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="18" t="s">
         <v>120</v>
       </c>
@@ -13910,7 +13910,7 @@
       </c>
       <c r="D189" s="14"/>
     </row>
-    <row r="190" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="18" t="s">
         <v>120</v>
       </c>
@@ -13922,7 +13922,7 @@
       </c>
       <c r="D190" s="14"/>
     </row>
-    <row r="191" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="18" t="s">
         <v>120</v>
       </c>
@@ -13934,7 +13934,7 @@
       </c>
       <c r="D191" s="14"/>
     </row>
-    <row r="192" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="18" t="s">
         <v>120</v>
       </c>
@@ -13946,13 +13946,13 @@
       </c>
       <c r="D192" s="14"/>
     </row>
-    <row r="193" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="18"/>
       <c r="B193" s="18"/>
       <c r="C193" s="14"/>
       <c r="D193" s="14"/>
     </row>
-    <row r="194" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="18" t="s">
         <v>129</v>
       </c>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="D194" s="14"/>
     </row>
-    <row r="195" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="18" t="s">
         <v>129</v>
       </c>
@@ -13976,7 +13976,7 @@
       </c>
       <c r="D195" s="14"/>
     </row>
-    <row r="196" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="18" t="s">
         <v>129</v>
       </c>
@@ -13988,7 +13988,7 @@
       </c>
       <c r="D196" s="14"/>
     </row>
-    <row r="197" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="18" t="s">
         <v>129</v>
       </c>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="D197" s="14"/>
     </row>
-    <row r="198" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="18" t="s">
         <v>129</v>
       </c>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="D198" s="14"/>
     </row>
-    <row r="199" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="18" t="s">
         <v>129</v>
       </c>
@@ -14024,7 +14024,7 @@
       </c>
       <c r="D199" s="14"/>
     </row>
-    <row r="200" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="18" t="s">
         <v>129</v>
       </c>
@@ -14036,7 +14036,7 @@
       </c>
       <c r="D200" s="14"/>
     </row>
-    <row r="201" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="18" t="s">
         <v>129</v>
       </c>
@@ -14048,7 +14048,7 @@
       </c>
       <c r="D201" s="14"/>
     </row>
-    <row r="202" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="18" t="s">
         <v>129</v>
       </c>
@@ -14060,7 +14060,7 @@
       </c>
       <c r="D202" s="14"/>
     </row>
-    <row r="203" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="18" t="s">
         <v>129</v>
       </c>
@@ -14072,7 +14072,7 @@
       </c>
       <c r="D203" s="14"/>
     </row>
-    <row r="204" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="18" t="s">
         <v>129</v>
       </c>
@@ -14084,7 +14084,7 @@
       </c>
       <c r="D204" s="14"/>
     </row>
-    <row r="205" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="18" t="s">
         <v>129</v>
       </c>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="D205" s="14"/>
     </row>
-    <row r="206" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="18" t="s">
         <v>129</v>
       </c>
@@ -14108,7 +14108,7 @@
       </c>
       <c r="D206" s="14"/>
     </row>
-    <row r="207" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="18" t="s">
         <v>129</v>
       </c>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="D207" s="14"/>
     </row>
-    <row r="208" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="18" t="s">
         <v>129</v>
       </c>
@@ -14132,13 +14132,13 @@
       </c>
       <c r="D208" s="14"/>
     </row>
-    <row r="209" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="18"/>
       <c r="B209" s="18"/>
       <c r="C209" s="14"/>
       <c r="D209" s="14"/>
     </row>
-    <row r="210" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="18" t="s">
         <v>145</v>
       </c>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="D210" s="14"/>
     </row>
-    <row r="211" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="18" t="s">
         <v>145</v>
       </c>
@@ -14162,13 +14162,13 @@
       </c>
       <c r="D211" s="14"/>
     </row>
-    <row r="212" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="18"/>
       <c r="B212" s="18"/>
       <c r="C212" s="14"/>
       <c r="D212" s="14"/>
     </row>
-    <row r="213" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="18" t="s">
         <v>148</v>
       </c>
@@ -14180,7 +14180,7 @@
       </c>
       <c r="D213" s="14"/>
     </row>
-    <row r="214" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="18" t="s">
         <v>148</v>
       </c>
@@ -14192,7 +14192,7 @@
       </c>
       <c r="D214" s="14"/>
     </row>
-    <row r="215" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="18" t="s">
         <v>148</v>
       </c>
@@ -14204,7 +14204,7 @@
       </c>
       <c r="D215" s="14"/>
     </row>
-    <row r="216" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="18" t="s">
         <v>148</v>
       </c>
@@ -14216,7 +14216,7 @@
       </c>
       <c r="D216" s="14"/>
     </row>
-    <row r="217" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="18" t="s">
         <v>148</v>
       </c>
@@ -14228,7 +14228,7 @@
       </c>
       <c r="D217" s="14"/>
     </row>
-    <row r="218" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="18" t="s">
         <v>148</v>
       </c>
@@ -14240,7 +14240,7 @@
       </c>
       <c r="D218" s="14"/>
     </row>
-    <row r="219" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="18" t="s">
         <v>148</v>
       </c>
@@ -14252,7 +14252,7 @@
       </c>
       <c r="D219" s="14"/>
     </row>
-    <row r="220" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="18" t="s">
         <v>148</v>
       </c>
@@ -14264,7 +14264,7 @@
       </c>
       <c r="D220" s="14"/>
     </row>
-    <row r="221" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="18" t="s">
         <v>148</v>
       </c>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="D221" s="14"/>
     </row>
-    <row r="222" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="18" t="s">
         <v>148</v>
       </c>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="D222" s="14"/>
     </row>
-    <row r="223" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="18" t="s">
         <v>148</v>
       </c>
@@ -14300,7 +14300,7 @@
       </c>
       <c r="D223" s="14"/>
     </row>
-    <row r="224" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="18" t="s">
         <v>148</v>
       </c>
@@ -14312,7 +14312,7 @@
       </c>
       <c r="D224" s="14"/>
     </row>
-    <row r="225" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="18" t="s">
         <v>148</v>
       </c>
@@ -14324,7 +14324,7 @@
       </c>
       <c r="D225" s="14"/>
     </row>
-    <row r="226" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="18" t="s">
         <v>148</v>
       </c>
@@ -14336,7 +14336,7 @@
       </c>
       <c r="D226" s="14"/>
     </row>
-    <row r="227" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="18" t="s">
         <v>148</v>
       </c>
@@ -14348,7 +14348,7 @@
       </c>
       <c r="D227" s="14"/>
     </row>
-    <row r="228" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="18" t="s">
         <v>148</v>
       </c>
@@ -14360,7 +14360,7 @@
       </c>
       <c r="D228" s="14"/>
     </row>
-    <row r="229" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="18" t="s">
         <v>148</v>
       </c>
@@ -14374,28 +14374,28 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="F158:F159"/>
+    <mergeCell ref="F161:F162"/>
+    <mergeCell ref="F163:F165"/>
+    <mergeCell ref="F106:F107"/>
+    <mergeCell ref="F118:F119"/>
+    <mergeCell ref="F114:F115"/>
+    <mergeCell ref="F88:F90"/>
+    <mergeCell ref="F86:F87"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="F156:F157"/>
+    <mergeCell ref="F153:F154"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="F24:F26"/>
     <mergeCell ref="F40:F41"/>
     <mergeCell ref="F50:F51"/>
     <mergeCell ref="F31:F34"/>
     <mergeCell ref="F27:F30"/>
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="F43:F44"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F19:F21"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="F88:F90"/>
-    <mergeCell ref="F86:F87"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="F156:F157"/>
-    <mergeCell ref="F153:F154"/>
-    <mergeCell ref="F158:F159"/>
-    <mergeCell ref="F161:F162"/>
-    <mergeCell ref="F163:F165"/>
-    <mergeCell ref="F106:F107"/>
-    <mergeCell ref="F118:F119"/>
-    <mergeCell ref="F114:F115"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14404,18 +14404,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB315A03-E31D-411F-9698-33ACCE886156}">
   <dimension ref="A1:AA90"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" customWidth="1"/>
-    <col min="4" max="4" width="36.85546875" customWidth="1"/>
-    <col min="16" max="18" width="9.140625" customWidth="1"/>
-    <col min="19" max="19" width="11.140625" customWidth="1"/>
-    <col min="20" max="24" width="9.140625" customWidth="1"/>
-    <col min="27" max="27" width="23.28515625" customWidth="1"/>
+    <col min="1" max="1" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="4" max="4" width="36.88671875" customWidth="1"/>
+    <col min="16" max="18" width="9.109375" customWidth="1"/>
+    <col min="19" max="19" width="11.109375" customWidth="1"/>
+    <col min="20" max="24" width="9.109375" customWidth="1"/>
+    <col min="27" max="27" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="E1" t="s">
         <v>322</v>
       </c>
@@ -14426,7 +14426,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>325</v>
       </c>
@@ -14503,7 +14503,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -14563,7 +14563,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -14617,7 +14617,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -14674,7 +14674,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -14731,7 +14731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -14788,7 +14788,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -14833,7 +14833,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -14896,7 +14896,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -14950,7 +14950,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -15010,7 +15010,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -15076,7 +15076,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -15142,7 +15142,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -15190,7 +15190,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -15256,7 +15256,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -15322,7 +15322,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>15</v>
       </c>
@@ -15367,7 +15367,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>16</v>
       </c>
@@ -15418,7 +15418,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>17</v>
       </c>
@@ -15469,7 +15469,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>18</v>
       </c>
@@ -15520,7 +15520,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>19</v>
       </c>
@@ -15568,7 +15568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
@@ -15613,7 +15613,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>21</v>
       </c>
@@ -15658,7 +15658,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>22</v>
       </c>
@@ -15709,7 +15709,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>23</v>
       </c>
@@ -15760,7 +15760,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>24</v>
       </c>
@@ -15805,7 +15805,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>25</v>
       </c>
@@ -15853,7 +15853,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26</v>
       </c>
@@ -15907,7 +15907,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>27</v>
       </c>
@@ -15952,7 +15952,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>28</v>
       </c>
@@ -15997,7 +15997,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>29</v>
       </c>
@@ -16042,7 +16042,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>30</v>
       </c>
@@ -16093,7 +16093,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>31</v>
       </c>
@@ -16141,7 +16141,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>32</v>
       </c>
@@ -16186,7 +16186,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>33</v>
       </c>
@@ -16231,7 +16231,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>34</v>
       </c>
@@ -16276,7 +16276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>35</v>
       </c>
@@ -16321,7 +16321,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>36</v>
       </c>
@@ -16366,7 +16366,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>37</v>
       </c>
@@ -16411,7 +16411,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>38</v>
       </c>
@@ -16483,7 +16483,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>39</v>
       </c>
@@ -16540,7 +16540,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>40</v>
       </c>
@@ -16603,7 +16603,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>41</v>
       </c>
@@ -16666,7 +16666,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>42</v>
       </c>
@@ -16720,7 +16720,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>43</v>
       </c>
@@ -16774,7 +16774,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>44</v>
       </c>
@@ -16819,7 +16819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>45</v>
       </c>
@@ -16864,7 +16864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>46</v>
       </c>
@@ -16933,7 +16933,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>47</v>
       </c>
@@ -17005,7 +17005,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>48</v>
       </c>
@@ -17056,7 +17056,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>49</v>
       </c>
@@ -17125,7 +17125,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>50</v>
       </c>
@@ -17170,7 +17170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>51</v>
       </c>
@@ -17224,7 +17224,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>52</v>
       </c>
@@ -17269,7 +17269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>53</v>
       </c>
@@ -17317,7 +17317,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>54</v>
       </c>
@@ -17386,7 +17386,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>55</v>
       </c>
@@ -17431,7 +17431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>56</v>
       </c>
@@ -17482,7 +17482,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>57</v>
       </c>
@@ -17536,7 +17536,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>58</v>
       </c>
@@ -17581,7 +17581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>59</v>
       </c>
@@ -17629,7 +17629,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>60</v>
       </c>
@@ -17674,7 +17674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="114.75" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25" ht="118.8" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>61</v>
       </c>
@@ -17749,7 +17749,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25" ht="66" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>62</v>
       </c>
@@ -17800,7 +17800,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" ht="66" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>63</v>
       </c>
@@ -17845,7 +17845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>64</v>
       </c>
@@ -17890,7 +17890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>65</v>
       </c>
@@ -17935,7 +17935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" ht="66" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>66</v>
       </c>
@@ -17980,7 +17980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>67</v>
       </c>
@@ -18025,7 +18025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>68</v>
       </c>
@@ -18070,7 +18070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>69</v>
       </c>
@@ -18115,7 +18115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>70</v>
       </c>
@@ -18160,7 +18160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>71</v>
       </c>
@@ -18205,7 +18205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>72</v>
       </c>
@@ -18250,7 +18250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>73</v>
       </c>
@@ -18295,7 +18295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>74</v>
       </c>
@@ -18340,7 +18340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>75</v>
       </c>
@@ -18385,7 +18385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>76</v>
       </c>
@@ -18430,7 +18430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>77</v>
       </c>
@@ -18475,7 +18475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>78</v>
       </c>
@@ -18520,7 +18520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="76.5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" ht="79.2" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>79</v>
       </c>
@@ -18565,7 +18565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>80</v>
       </c>
@@ -18640,7 +18640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>81</v>
       </c>
@@ -18685,7 +18685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>82</v>
       </c>
@@ -18730,7 +18730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>83</v>
       </c>
@@ -18793,7 +18793,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>84</v>
       </c>
@@ -18838,7 +18838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>85</v>
       </c>
@@ -18883,7 +18883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>86</v>
       </c>
@@ -18928,7 +18928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>87</v>
       </c>
@@ -18973,7 +18973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>88</v>
       </c>
